--- a/Data/SangamPeriod.xlsx
+++ b/Data/SangamPeriod.xlsx
@@ -472,2599 +472,2599 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which occupation was highly respected during the Sangam period?</t>
+          <t>Which Sangam king is believed to have imprisoned a Yavana trader?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pottery</t>
+          <t>Senguttuvan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Karikala</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Nedunjeliyan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Perunarkilli</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Nedunjeliyan</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which metal was predominantly used for coinage during the Sangam Age?</t>
+          <t>Which river was important to the Chera kingdom?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Kaveri</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Vaigai</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Periyar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Pamba</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Periyar</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tolkappiyam, a major work of Sangam literature, is primarily a treatise on:</t>
+          <t>The Sangam literature was composed in which language?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Medicine</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Grammar</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Astronomy</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Grammar</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The term 'Aram' in Sangam texts refers to:</t>
+          <t>The city of Madurai is considered to be the center of which Sangam?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wealth</t>
+          <t>First</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>Second</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethics</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
+          <t>Third</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ethics</t>
+          <t>Third</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Sangam literature is divided into:</t>
+          <t>Which Sangam king defeated the combined forces of Cheras and Pandyas?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Religious &amp; Scientific</t>
+          <t>Karikala Chola</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Historical &amp; Fictional</t>
+          <t>Senguttuvan</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Akam &amp; Puram</t>
+          <t>Perunarkilli</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>North &amp; South</t>
+          <t>Nedunjeliyan</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Akam &amp; Puram</t>
+          <t>Karikala Chola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which was the famous port of the Pandya kingdom?</t>
+          <t>Which of the following cities was submerged according to Sangam tradition?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uraiyur</t>
+          <t>Kanchi</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tondi</t>
+          <t>Puhar</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Korkai</t>
+          <t>Dwaraka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mamallapuram</t>
+          <t>Kumari Kandam</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Korkai</t>
+          <t>Kumari Kandam</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which Sangam text includes love poems?</t>
+          <t>What type of marriage was preferred in Sangam society?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Purananuru</t>
+          <t>Arranged</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>Swayamvara</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Akananuru</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tolkappiyam</t>
+          <t>Endogamy</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Akananuru</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The rulers of which dynasty used the bow and arrow as their emblem?</t>
+          <t>What was the main theme of the text 'Purapporul Venba Malai'?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cholas</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pandyas</t>
+          <t>War</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cheras</t>
+          <t>Poetics</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Satavahanas</t>
+          <t>Grammar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cheras</t>
+          <t>War</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>How many Sangams are believed to have existed in ancient Tamil history?</t>
+          <t>Which poem describes the city of Puhar in detail?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Pattinappalai</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Paripadal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Pattinappalai</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>'Akam' poetry deals with themes of:</t>
+          <t>The famous Tamil epic 'Silappatikaram' was composed by:</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>War and Valor</t>
+          <t>Ilango Adigal</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Love and Emotion</t>
+          <t>Avvaiyar</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Religious Hymns</t>
+          <t>Tolkappiyar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Moral Ethics</t>
+          <t>Sattanar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Love and Emotion</t>
+          <t>Ilango Adigal</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which foreign power established trade with Sangam-era Tamilakam?</t>
+          <t>Which king performed a “Rajasuyam” as per Sangam records?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portuguese</t>
+          <t>Nedunjeliyan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Greeks</t>
+          <t>Senguttuvan</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>Karikala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dutch</t>
+          <t>Perunarkilli</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Greeks</t>
+          <t>Perunarkilli</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The famous Tamil epic 'Silappatikaram' was composed by:</t>
+          <t>What was the term for land taxes in Sangam administration?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ilango Adigal</t>
+          <t>Irai</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Avvaiyar</t>
+          <t>Bhaga</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tolkappiyar</t>
+          <t>Bali</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sattanar</t>
+          <t>Vetti</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ilango Adigal</t>
+          <t>Irai</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which Sangam work describes the five-fold classification of land?</t>
+          <t>The Sangam literature is divided into:</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>Religious &amp; Scientific</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Purananuru</t>
+          <t>Historical &amp; Fictional</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tolkappiyam</t>
+          <t>Akam &amp; Puram</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Akananuru</t>
+          <t>North &amp; South</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tolkappiyam</t>
+          <t>Akam &amp; Puram</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Chera king Senguttuvan is associated with which legendary event?</t>
+          <t>The earliest mention of Tamil culture in foreign sources was by:</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Battle of Kalinga</t>
+          <t>Herodotus</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ratha Yatra</t>
+          <t>Pliny the Elder</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Worship of Kannagi</t>
+          <t>Ptolemy</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Battle of Hydaspes</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Worship of Kannagi</t>
+          <t>Pliny the Elder</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which Sangam text deals with the ethics of life and is compared to the Gita?</t>
+          <t>The Chera king Senguttuvan is associated with which legendary event?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Purananuru</t>
+          <t>Battle of Kalinga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tolkappiyam</t>
+          <t>Ratha Yatra</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>Worship of Kannagi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>Battle of Hydaspes</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>Worship of Kannagi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which foreign group is mentioned in Sangam texts as "Yavanas"?</t>
+          <t>Who among the following composed war poems during the Sangam era?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greeks</t>
+          <t>Avvaiyar</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Romans</t>
+          <t>Kambar</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>Kalidasa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arabs</t>
+          <t>Bharavi</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Greeks</t>
+          <t>Avvaiyar</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which Sangam king defeated the combined forces of Cheras and Pandyas?</t>
+          <t>Which class dominated Sangam politics and economy?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Karikala Chola</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Senguttuvan</t>
+          <t>Kshatriyas</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Perunarkilli</t>
+          <t>Velirs</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nedunjeliyan</t>
+          <t>Merchants</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Karikala Chola</t>
+          <t>Velirs</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The symbol of the Chola dynasty was:</t>
+          <t>Which Sangam text contains information about the ideal king and his duties?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Purananuru</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bow</t>
+          <t>Tolkappiyam</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Pattinappalai</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Purananuru</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which of the following was a famous Sangam port city?</t>
+          <t>Which metal was predominantly used for coinage during the Sangam Age?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kanchipuram</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Puhar</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Madurai</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Puhar</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Who was the famous poetess of the Sangam period?</t>
+          <t>The symbol of the Chola dynasty was:</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avvaiyar</t>
+          <t>Fish</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Kalidasa</t>
+          <t>Bow</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gargi</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vishaka</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Avvaiyar</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which Sangam king is said to have fed all poets in his court?</t>
+          <t>Which deity is most often praised in 'Paripadal'?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Karikala</t>
+          <t>Murugan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Nedunjeliyan</t>
+          <t>Shiva</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Uthiyan Cheralathan</t>
+          <t>Vishnu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Perunarkilli</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Uthiyan Cheralathan</t>
+          <t>Vishnu</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The term 'Muvendar' refers to:</t>
+          <t>The Sangam assemblies were held in which temple?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Three gods</t>
+          <t>Meenakshi Temple</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Three ports</t>
+          <t>Madurai Sangam Hall</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Three kings</t>
+          <t>Koodal Azhagar Temple</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Three texts</t>
+          <t>Thiruparankundram</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Three kings</t>
+          <t>Koodal Azhagar Temple</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which of the following was a chief occupation of the people in the Sangam age?</t>
+          <t>Which Sangam text describes trade activities in detail?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Blacksmithing</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Pattinappalai</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gold Mining</t>
+          <t>Akananuru</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shipbuilding</t>
+          <t>Tolkappiyam</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Pattinappalai</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which foreign group were the "Yavanas" known for in Tamilakam?</t>
+          <t>The concept of 'Thinai' in Sangam literature relates to:</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>Weapons</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Landscape poetry</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>Trade</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Warfare</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Philosophy</t>
+          <t>Social caste</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Landscape poetry</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The capital of the early Pandya kingdom during the Sangam age was:</t>
+          <t>Which Sangam king is credited with conquering Sri Lanka?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kanchipuram</t>
+          <t>Karikala Chola</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Madurai</t>
+          <t>Nedunjeliyan</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Uraiyur</t>
+          <t>Senguttuvan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vanji</t>
+          <t>Uthiyan Cheralathan</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Madurai</t>
+          <t>Karikala Chola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which Sangam port had Roman amphorae and coins excavated?</t>
+          <t>Which occupation was highly respected during the Sangam period?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Puhar</t>
+          <t>Pottery</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Korkai</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tondi</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arikamedu</t>
+          <t>Fishing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Arikamedu</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Sangam period roughly corresponds to which time frame?</t>
+          <t>The Sangam age saw the use of which script?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1000 BCE – 500 BCE</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>300 BCE – 300 CE</t>
+          <t>Grantha</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>600 CE – 900 CE</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>900 CE – 1200 CE</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>300 BCE – 300 CE</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Sangam literature was composed in which language?</t>
+          <t>The term 'Aram' in Sangam texts refers to:</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Wealth</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Ethics</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Ethics</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The earliest mention of Tamil culture in foreign sources was by:</t>
+          <t>What was the role of 'Arasu' in Sangam polity?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Herodotus</t>
+          <t>Poet</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Pliny the Elder</t>
+          <t>Judge</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ptolemy</t>
+          <t>King</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Priest</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pliny the Elder</t>
+          <t>King</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which river was important to the Chera kingdom?</t>
+          <t>Which Sangam port had Roman amphorae and coins excavated?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kaveri</t>
+          <t>Puhar</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Vaigai</t>
+          <t>Korkai</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Periyar</t>
+          <t>Tondi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pamba</t>
+          <t>Arikamedu</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Periyar</t>
+          <t>Arikamedu</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>What was the term for land taxes in Sangam administration?</t>
+          <t>Which Sangam age king was known as "Imayavaramban"?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irai</t>
+          <t>Karikala Chola</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Bhaga</t>
+          <t>Senguttuvan</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Nedunjeliyan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vetti</t>
+          <t>Uthiyan Cheralathan</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Irai</t>
+          <t>Senguttuvan</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which deity is most often praised in 'Paripadal'?</t>
+          <t>Which was the famous port of the Pandya kingdom?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Murugan</t>
+          <t>Uraiyur</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Shiva</t>
+          <t>Tondi</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vishnu</t>
+          <t>Korkai</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Mamallapuram</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Vishnu</t>
+          <t>Korkai</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Sangam text 'Aingurunuru' belongs to which category?</t>
+          <t>Who among the following was NOT a Sangam poet?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Kapilar</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Grammar</t>
+          <t>Avvaiyar</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Poetry</t>
+          <t>Ilango Adigal</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Drama</t>
+          <t>Banabhatta</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poetry</t>
+          <t>Banabhatta</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which work mentions the great floods that submerged the first Sangam?</t>
+          <t>Which Sangam text includes love poems?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>Purananuru</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>Thirukkural</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Silappatikaram</t>
-        </is>
-      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Iraiyanar Agapporul</t>
+          <t>Akananuru</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kalithogai</t>
+          <t>Tolkappiyam</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Iraiyanar Agapporul</t>
+          <t>Akananuru</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sangam poems were compiled into:</t>
+          <t>Which literary work gives an account of Karikala Chola’s rule?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>10 major works</t>
+          <t>Manimekalai</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5 minor works</t>
+          <t>Pattinappalai</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>18 major works</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>12 minor works</t>
+          <t>Paripadal</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>18 major works</t>
+          <t>Pattinappalai</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which Sangam king is believed to have imprisoned a Yavana trader?</t>
+          <t>The capital of the early Pandya kingdom during the Sangam age was:</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Senguttuvan</t>
+          <t>Kanchipuram</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Karikala</t>
+          <t>Madurai</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nedunjeliyan</t>
+          <t>Uraiyur</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Perunarkilli</t>
+          <t>Vanji</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nedunjeliyan</t>
+          <t>Madurai</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which landscape type is associated with lovers' separation in Sangam poetry?</t>
+          <t>'Paripadal' is a Sangam text devoted to:</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Palai</t>
+          <t>Heroism</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Kurinji</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mullai</t>
+          <t>Religious hymns</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Marutham</t>
+          <t>Politics</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Palai</t>
+          <t>Religious hymns</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The term 'Vanigar' in Sangam texts refers to:</t>
+          <t>Which of the following Tamil kingdoms was not part of the 'Muvendar'?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Soldiers</t>
+          <t>Cheras</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Merchants</t>
+          <t>Cholas</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Poets</t>
+          <t>Pandyas</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Pallavas</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Merchants</t>
+          <t>Pallavas</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which Sangam text describes trade activities in detail?</t>
+          <t>Which of the following was a famous Sangam port city?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>Kanchipuram</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Pattinappalai</t>
+          <t>Puhar</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Akananuru</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tolkappiyam</t>
+          <t>Madurai</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pattinappalai</t>
+          <t>Puhar</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which Sangam text is entirely devoted to the praise of kings and warfare?</t>
+          <t>What was the title of the Chola king Karikala?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Akananuru</t>
+          <t>Vanavan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Kalithogai</t>
+          <t>Imayavaramban</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Purananuru</t>
+          <t>Senguttuvan</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>Karikalan</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Purananuru</t>
+          <t>Karikalan</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The most commonly mentioned god in Sangam literature is:</t>
+          <t>The rulers of which dynasty used the bow and arrow as their emblem?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Vishnu</t>
+          <t>Cholas</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Shiva</t>
+          <t>Pandyas</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Murugan</t>
+          <t>Cheras</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brahma</t>
+          <t>Satavahanas</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Murugan</t>
+          <t>Cheras</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Who among the following was NOT a Sangam poet?</t>
+          <t>Which work mentions the great floods that submerged the first Sangam?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kapilar</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Avvaiyar</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ilango Adigal</t>
+          <t>Iraiyanar Agapporul</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Banabhatta</t>
+          <t>Kalithogai</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Banabhatta</t>
+          <t>Iraiyanar Agapporul</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The Sangam period saw trade with which Roman Emperor's era?</t>
+          <t>Which Sangam text deals with the ethics of life and is compared to the Gita?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nero</t>
+          <t>Purananuru</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Augustus</t>
+          <t>Tolkappiyam</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Constantine</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trajan</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Augustus</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which Tamil epic narrates the story of Kovalan and Kannagi?</t>
+          <t>The term 'Muvendar' refers to:</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>Three gods</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>Three ports</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Manimekalai</t>
+          <t>Three kings</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Pattinappalai</t>
+          <t>Three texts</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>Three kings</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which of the following cities was submerged according to Sangam tradition?</t>
+          <t>Which god is associated with the 'Kurinji' landscape in Sangam poetry?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kanchi</t>
+          <t>Vishnu</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Puhar</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dwaraka</t>
+          <t>Murugan</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kumari Kandam</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Kumari Kandam</t>
+          <t>Murugan</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which Sangam poet was known as the 'Friend of Nature'?</t>
+          <t>Which title did Chola kings often use?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avvaiyar</t>
+          <t>Satyavadi</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Kapilar</t>
+          <t>Vanavan</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nakkeerar</t>
+          <t>Imayavaramban</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ilango Adigal</t>
+          <t>Chakravarti</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Kapilar</t>
+          <t>Vanavan</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>What was the role of 'Arasu' in Sangam polity?</t>
+          <t>Which of the following was a chief occupation of the people in the Sangam age?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Poet</t>
+          <t>Blacksmithing</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Judge</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>King</t>
+          <t>Gold Mining</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Priest</t>
+          <t>Shipbuilding</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>King</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which title did Chola kings often use?</t>
+          <t>The most commonly mentioned god in Sangam literature is:</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Satyavadi</t>
+          <t>Vishnu</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Vanavan</t>
+          <t>Shiva</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Imayavaramban</t>
+          <t>Murugan</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Chakravarti</t>
+          <t>Brahma</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Vanavan</t>
+          <t>Murugan</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Who was the author of 'Manimekalai'?</t>
+          <t>The Sangam period saw trade with which Roman Emperor's era?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ilango Adigal</t>
+          <t>Nero</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Avvaiyar</t>
+          <t>Augustus</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sattanar</t>
+          <t>Constantine</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tolkappiyar</t>
+          <t>Trajan</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sattanar</t>
+          <t>Augustus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The concept of 'Thinai' in Sangam literature relates to:</t>
+          <t>Which concept in Sangam poetry represents external experience like war, politics?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Weapons</t>
+          <t>Akam</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Landscape poetry</t>
+          <t>Puram</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Bhakti</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Social caste</t>
+          <t>Aram</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Landscape poetry</t>
+          <t>Puram</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>'Paripadal' is a Sangam text devoted to:</t>
+          <t>Tolkappiyam, a major work of Sangam literature, is primarily a treatise on:</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Heroism</t>
+          <t>Medicine</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>Politics</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Religious hymns</t>
+          <t>Grammar</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Astronomy</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Religious hymns</t>
+          <t>Grammar</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which Sangam dynasty had its capital at Uraiyur?</t>
+          <t>The Sangam period roughly corresponds to which time frame?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cheras</t>
+          <t>1000 BCE – 500 BCE</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Pandyas</t>
+          <t>300 BCE – 300 CE</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Cholas</t>
+          <t>600 CE – 900 CE</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Pallavas</t>
+          <t>900 CE – 1200 CE</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cholas</t>
+          <t>300 BCE – 300 CE</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The Tamil work 'Manimekalai' is a sequel to:</t>
+          <t>Which Sangam dynasty had its capital at Uraiyur?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>Cheras</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Pattinappalai</t>
+          <t>Pandyas</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>Cholas</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tolkappiyam</t>
+          <t>Pallavas</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>Cholas</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which concept in Sangam poetry represents external experience like war, politics?</t>
+          <t>Which Sangam king is said to have fed all poets in his court?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Akam</t>
+          <t>Karikala</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Puram</t>
+          <t>Nedunjeliyan</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bhakti</t>
+          <t>Uthiyan Cheralathan</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Aram</t>
+          <t>Perunarkilli</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Puram</t>
+          <t>Uthiyan Cheralathan</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>The Sangam assemblies were held in which temple?</t>
+          <t>Which landscape type is associated with lovers' separation in Sangam poetry?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Meenakshi Temple</t>
+          <t>Palai</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Madurai Sangam Hall</t>
+          <t>Kurinji</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Koodal Azhagar Temple</t>
+          <t>Mullai</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Thiruparankundram</t>
+          <t>Marutham</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Koodal Azhagar Temple</t>
+          <t>Palai</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The chief port of the Cholas during the Sangam period was:</t>
+          <t>Which Sangam text is entirely devoted to the praise of kings and warfare?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Puhar</t>
+          <t>Akananuru</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Madurai</t>
+          <t>Kalithogai</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Tondi</t>
+          <t>Purananuru</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Korkai</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Puhar</t>
+          <t>Purananuru</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>What was the title of the Chola king Karikala?</t>
+          <t>Which foreign group is mentioned in Sangam texts as "Yavanas"?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Vanavan</t>
+          <t>Greeks</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Imayavaramban</t>
+          <t>Romans</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Senguttuvan</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Karikalan</t>
+          <t>Arabs</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Karikalan</t>
+          <t>Greeks</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which Sangam age king was known as "Imayavaramban"?</t>
+          <t>The term 'Vanigar' in Sangam texts refers to:</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Karikala Chola</t>
+          <t>Soldiers</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Senguttuvan</t>
+          <t>Merchants</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Nedunjeliyan</t>
+          <t>Poets</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Uthiyan Cheralathan</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Senguttuvan</t>
+          <t>Merchants</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Sangam age saw the use of which script?</t>
+          <t>How many Sangams are believed to have existed in ancient Tamil history?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Grantha</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The term 'Velir' refers to:</t>
+          <t>The Sangam text 'Aingurunuru' belongs to which category?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Commoners</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Feudal chieftains</t>
+          <t>Grammar</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Poetry</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Slaves</t>
+          <t>Drama</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Feudal chieftains</t>
+          <t>Poetry</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>What was the main theme of the text 'Purapporul Venba Malai'?</t>
+          <t>Which region is associated with the 'Mullai' landscape in Sangam literature?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>Mountains</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>War</t>
+          <t>Forest</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Poetics</t>
+          <t>Farmland</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grammar</t>
+          <t>Coast</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>War</t>
+          <t>Forest</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which literary work gives an account of Karikala Chola’s rule?</t>
+          <t>Which Sangam poet was known as the 'Friend of Nature'?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Manimekalai</t>
+          <t>Avvaiyar</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Pattinappalai</t>
+          <t>Kapilar</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>Nakkeerar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Paripadal</t>
+          <t>Ilango Adigal</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pattinappalai</t>
+          <t>Kapilar</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Who among the following composed war poems during the Sangam era?</t>
+          <t>Which foreign power established trade with Sangam-era Tamilakam?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avvaiyar</t>
+          <t>Portuguese</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Kambar</t>
+          <t>Greeks</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kalidasa</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bharavi</t>
+          <t>Dutch</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Avvaiyar</t>
+          <t>Greeks</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which region is associated with the 'Mullai' landscape in Sangam literature?</t>
+          <t>Who was the famous poetess of the Sangam period?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Mountains</t>
+          <t>Avvaiyar</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Kalidasa</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Farmland</t>
+          <t>Gargi</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Vishaka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Avvaiyar</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which of the following Tamil kingdoms was not part of the 'Muvendar'?</t>
+          <t>The Tamil work 'Manimekalai' is a sequel to:</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cheras</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Cholas</t>
+          <t>Pattinappalai</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Pandyas</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pallavas</t>
+          <t>Tolkappiyam</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pallavas</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which king performed a “Rajasuyam” as per Sangam records?</t>
+          <t>The chief port of the Cholas during the Sangam period was:</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Nedunjeliyan</t>
+          <t>Puhar</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Senguttuvan</t>
+          <t>Madurai</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Karikala</t>
+          <t>Tondi</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Perunarkilli</t>
+          <t>Korkai</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Perunarkilli</t>
+          <t>Puhar</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The city of Madurai is considered to be the center of which Sangam?</t>
+          <t>Who was the author of 'Manimekalai'?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>First</t>
+          <t>Ilango Adigal</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Second</t>
+          <t>Avvaiyar</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Third</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
+          <t>Sattanar</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tolkappiyar</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Third</t>
+          <t>Sattanar</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which class dominated Sangam politics and economy?</t>
+          <t>'Akam' poetry deals with themes of:</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>War and Valor</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Kshatriyas</t>
+          <t>Love and Emotion</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Velirs</t>
+          <t>Religious Hymns</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Merchants</t>
+          <t>Moral Ethics</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Velirs</t>
+          <t>Love and Emotion</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which god is associated with the 'Kurinji' landscape in Sangam poetry?</t>
+          <t>Which foreign group were the "Yavanas" known for in Tamilakam?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Vishnu</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Murugan</t>
+          <t>Warfare</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Philosophy</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Murugan</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>What type of marriage was preferred in Sangam society?</t>
+          <t>Which Tamil epic narrates the story of Kovalan and Kannagi?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Arranged</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Swayamvara</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>Manimekalai</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Endogamy</t>
+          <t>Pattinappalai</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which Sangam text contains information about the ideal king and his duties?</t>
+          <t>Which work mentions the story of a woman who burns down Madurai?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
+          <t>Thirukkural</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Manimekalai</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Silappatikaram</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t>Purananuru</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Tolkappiyam</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Pattinappalai</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Thirukkural</t>
-        </is>
-      </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Purananuru</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which poem describes the city of Puhar in detail?</t>
+          <t>Sangam poems were compiled into:</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>10 major works</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Pattinappalai</t>
+          <t>5 minor works</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Paripadal</t>
+          <t>18 major works</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>12 minor works</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pattinappalai</t>
+          <t>18 major works</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which work mentions the story of a woman who burns down Madurai?</t>
+          <t>Which Sangam work describes the five-fold classification of land?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3074,22 +3074,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Manimekalai</t>
+          <t>Purananuru</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>Tolkappiyam</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Purananuru</t>
+          <t>Akananuru</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>Tolkappiyam</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -3132,36 +3132,36 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which Sangam king is credited with conquering Sri Lanka?</t>
+          <t>The term 'Velir' refers to:</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Karikala Chola</t>
+          <t>Commoners</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Nedunjeliyan</t>
+          <t>Feudal chieftains</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Senguttuvan</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Uthiyan Cheralathan</t>
+          <t>Slaves</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Karikala Chola</t>
+          <t>Feudal chieftains</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>

--- a/Data/SangamPeriod.xlsx
+++ b/Data/SangamPeriod.xlsx
@@ -472,315 +472,319 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which Sangam king is believed to have imprisoned a Yavana trader?</t>
+          <t>Tolkappiyam, a major work of Sangam literature, is primarily a treatise on:</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Senguttuvan</t>
+          <t>Medicine</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Karikala</t>
+          <t>Politics</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nedunjeliyan</t>
+          <t>Grammar</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Perunarkilli</t>
+          <t>Astronomy</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nedunjeliyan</t>
+          <t>Grammar</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which river was important to the Chera kingdom?</t>
+          <t>What type of marriage was preferred in Sangam society?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kaveri</t>
+          <t>Arranged</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Vaigai</t>
+          <t>Swayamvara</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Periyar</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pamba</t>
+          <t>Endogamy</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Periyar</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Sangam literature was composed in which language?</t>
+          <t>Which Sangam poet was known as the 'Friend of Nature'?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Avvaiyar</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kapilar</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Nakkeerar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Ilango Adigal</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Kapilar</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The city of Madurai is considered to be the center of which Sangam?</t>
+          <t>Which Sangam king is credited with conquering Sri Lanka?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>First</t>
+          <t>Karikala Chola</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Second</t>
+          <t>Nedunjeliyan</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Third</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>Senguttuvan</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Uthiyan Cheralathan</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Third</t>
+          <t>Karikala Chola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which Sangam king defeated the combined forces of Cheras and Pandyas?</t>
+          <t>Which concept in Sangam poetry represents external experience like war, politics?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Karikala Chola</t>
+          <t>Akam</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Senguttuvan</t>
+          <t>Puram</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Perunarkilli</t>
+          <t>Bhakti</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nedunjeliyan</t>
+          <t>Aram</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Karikala Chola</t>
+          <t>Puram</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which of the following cities was submerged according to Sangam tradition?</t>
+          <t>Which foreign group were the "Yavanas" known for in Tamilakam?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kanchi</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Puhar</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dwaraka</t>
+          <t>Warfare</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kumari Kandam</t>
+          <t>Philosophy</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Kumari Kandam</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>What type of marriage was preferred in Sangam society?</t>
+          <t>What was the term for land taxes in Sangam administration?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Arranged</t>
+          <t>Irai</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Swayamvara</t>
+          <t>Bhaga</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>Bali</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Endogamy</t>
+          <t>Vetti</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>Irai</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>What was the main theme of the text 'Purapporul Venba Malai'?</t>
+          <t>Sangam poems were compiled into:</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>10 major works</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>War</t>
+          <t>5 minor works</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Poetics</t>
+          <t>18 major works</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grammar</t>
+          <t>12 minor works</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>War</t>
+          <t>18 major works</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which poem describes the city of Puhar in detail?</t>
+          <t>Which literary work gives an account of Karikala Chola’s rule?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Manimekalai</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Pattinappalai</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Thirukkural</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Pattinappalai</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Paripadal</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -792,108 +796,108 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The famous Tamil epic 'Silappatikaram' was composed by:</t>
+          <t>The symbol of the Chola dynasty was:</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ilango Adigal</t>
+          <t>Fish</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Avvaiyar</t>
+          <t>Bow</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tolkappiyar</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sattanar</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ilango Adigal</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which king performed a “Rajasuyam” as per Sangam records?</t>
+          <t>The most commonly mentioned god in Sangam literature is:</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nedunjeliyan</t>
+          <t>Vishnu</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Senguttuvan</t>
+          <t>Shiva</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Karikala</t>
+          <t>Murugan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Perunarkilli</t>
+          <t>Brahma</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perunarkilli</t>
+          <t>Murugan</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>What was the term for land taxes in Sangam administration?</t>
+          <t>The chief port of the Cholas during the Sangam period was:</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irai</t>
+          <t>Puhar</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Bhaga</t>
+          <t>Madurai</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Tondi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vetti</t>
+          <t>Korkai</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Irai</t>
+          <t>Puhar</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -936,155 +940,155 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The earliest mention of Tamil culture in foreign sources was by:</t>
+          <t>Which work mentions the story of a woman who burns down Madurai?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Herodotus</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Pliny the Elder</t>
+          <t>Manimekalai</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ptolemy</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Purananuru</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pliny the Elder</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Chera king Senguttuvan is associated with which legendary event?</t>
+          <t>Which Sangam king defeated the combined forces of Cheras and Pandyas?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Battle of Kalinga</t>
+          <t>Karikala Chola</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ratha Yatra</t>
+          <t>Senguttuvan</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Worship of Kannagi</t>
+          <t>Perunarkilli</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Battle of Hydaspes</t>
+          <t>Nedunjeliyan</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Worship of Kannagi</t>
+          <t>Karikala Chola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Who among the following composed war poems during the Sangam era?</t>
+          <t>Which of the following was a famous Sangam port city?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avvaiyar</t>
+          <t>Kanchipuram</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Kambar</t>
+          <t>Puhar</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kalidasa</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bharavi</t>
+          <t>Madurai</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Avvaiyar</t>
+          <t>Puhar</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which class dominated Sangam politics and economy?</t>
+          <t>What was the title of the Chola king Karikala?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Vanavan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Kshatriyas</t>
+          <t>Imayavaramban</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Velirs</t>
+          <t>Senguttuvan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Merchants</t>
+          <t>Karikalan</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Velirs</t>
+          <t>Karikalan</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which Sangam text contains information about the ideal king and his duties?</t>
+          <t>Which Sangam text deals with the ethics of life and is compared to the Gita?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1099,218 +1103,218 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pattinappalai</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>Silappatikaram</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>Thirukkural</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Purananuru</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which metal was predominantly used for coinage during the Sangam Age?</t>
+          <t>Which class dominated Sangam politics and economy?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Kshatriyas</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Velirs</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Merchants</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Velirs</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The symbol of the Chola dynasty was:</t>
+          <t>Which god is associated with the 'Kurinji' landscape in Sangam poetry?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Vishnu</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Bow</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Murugan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Murugan</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which deity is most often praised in 'Paripadal'?</t>
+          <t>The term 'Muvendar' refers to:</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Murugan</t>
+          <t>Three gods</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Shiva</t>
+          <t>Three ports</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vishnu</t>
+          <t>Three kings</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Three texts</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Vishnu</t>
+          <t>Three kings</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Sangam assemblies were held in which temple?</t>
+          <t>The Sangam period saw trade with which Roman Emperor's era?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Meenakshi Temple</t>
+          <t>Nero</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Madurai Sangam Hall</t>
+          <t>Augustus</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Koodal Azhagar Temple</t>
+          <t>Constantine</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Thiruparankundram</t>
+          <t>Trajan</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Koodal Azhagar Temple</t>
+          <t>Augustus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which Sangam text describes trade activities in detail?</t>
+          <t>Which title did Chola kings often use?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>Satyavadi</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Pattinappalai</t>
+          <t>Vanavan</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Akananuru</t>
+          <t>Imayavaramban</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tolkappiyam</t>
+          <t>Chakravarti</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pattinappalai</t>
+          <t>Vanavan</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The concept of 'Thinai' in Sangam literature relates to:</t>
+          <t>Which occupation was highly respected during the Sangam period?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Weapons</t>
+          <t>Pottery</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Landscape poetry</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1320,156 +1324,156 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Social caste</t>
+          <t>Fishing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Landscape poetry</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which Sangam king is credited with conquering Sri Lanka?</t>
+          <t>Which Sangam text describes trade activities in detail?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Karikala Chola</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Nedunjeliyan</t>
+          <t>Pattinappalai</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Senguttuvan</t>
+          <t>Akananuru</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Uthiyan Cheralathan</t>
+          <t>Tolkappiyam</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Karikala Chola</t>
+          <t>Pattinappalai</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which occupation was highly respected during the Sangam period?</t>
+          <t>Which Tamil epic narrates the story of Kovalan and Kannagi?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pottery</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Manimekalai</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Pattinappalai</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Sangam age saw the use of which script?</t>
+          <t>Which Sangam text is entirely devoted to the praise of kings and warfare?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>Akananuru</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Grantha</t>
+          <t>Kalithogai</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Purananuru</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Purananuru</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The term 'Aram' in Sangam texts refers to:</t>
+          <t>Which Sangam poet was known for writing in praise of war heroes?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wealth</t>
+          <t>Kapilar</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>Paranar</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ethics</t>
+          <t>Nakkeerar</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Avvaiyar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ethics</t>
+          <t>Paranar</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -1548,1250 +1552,1250 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which Sangam age king was known as "Imayavaramban"?</t>
+          <t>Which foreign power established trade with Sangam-era Tamilakam?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Karikala Chola</t>
+          <t>Portuguese</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Senguttuvan</t>
+          <t>Greeks</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nedunjeliyan</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Uthiyan Cheralathan</t>
+          <t>Dutch</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Senguttuvan</t>
+          <t>Greeks</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which was the famous port of the Pandya kingdom?</t>
+          <t>Who among the following composed war poems during the Sangam era?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Uraiyur</t>
+          <t>Avvaiyar</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tondi</t>
+          <t>Kambar</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Korkai</t>
+          <t>Kalidasa</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mamallapuram</t>
+          <t>Bharavi</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Korkai</t>
+          <t>Avvaiyar</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Who among the following was NOT a Sangam poet?</t>
+          <t>Which of the following Tamil kingdoms was not part of the 'Muvendar'?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kapilar</t>
+          <t>Cheras</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Avvaiyar</t>
+          <t>Cholas</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ilango Adigal</t>
+          <t>Pandyas</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Banabhatta</t>
+          <t>Pallavas</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Banabhatta</t>
+          <t>Pallavas</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which Sangam text includes love poems?</t>
+          <t>Which Sangam age king was known as "Imayavaramban"?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Purananuru</t>
+          <t>Karikala Chola</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>Senguttuvan</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Akananuru</t>
+          <t>Nedunjeliyan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tolkappiyam</t>
+          <t>Uthiyan Cheralathan</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Akananuru</t>
+          <t>Senguttuvan</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which literary work gives an account of Karikala Chola’s rule?</t>
+          <t>Which region is associated with the 'Mullai' landscape in Sangam literature?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Manimekalai</t>
+          <t>Mountains</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Pattinappalai</t>
+          <t>Forest</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>Farmland</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Paripadal</t>
+          <t>Coast</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pattinappalai</t>
+          <t>Forest</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The capital of the early Pandya kingdom during the Sangam age was:</t>
+          <t>Who was the author of 'Manimekalai'?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kanchipuram</t>
+          <t>Ilango Adigal</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Madurai</t>
+          <t>Avvaiyar</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Uraiyur</t>
+          <t>Sattanar</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vanji</t>
+          <t>Tolkappiyar</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Madurai</t>
+          <t>Sattanar</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>'Paripadal' is a Sangam text devoted to:</t>
+          <t>The Sangam text 'Aingurunuru' belongs to which category?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Heroism</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>Grammar</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Religious hymns</t>
+          <t>Poetry</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Drama</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Religious hymns</t>
+          <t>Poetry</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which of the following Tamil kingdoms was not part of the 'Muvendar'?</t>
+          <t>The Tamil work 'Manimekalai' is a sequel to:</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cheras</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cholas</t>
+          <t>Pattinappalai</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pandyas</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pallavas</t>
+          <t>Tolkappiyam</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pallavas</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which of the following was a famous Sangam port city?</t>
+          <t>Which Sangam work describes the five-fold classification of land?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kanchipuram</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Puhar</t>
+          <t>Purananuru</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Tolkappiyam</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Madurai</t>
+          <t>Akananuru</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Puhar</t>
+          <t>Tolkappiyam</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>What was the title of the Chola king Karikala?</t>
+          <t>How many Sangams are believed to have existed in ancient Tamil history?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Vanavan</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Imayavaramban</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Senguttuvan</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Karikalan</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Karikalan</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The rulers of which dynasty used the bow and arrow as their emblem?</t>
+          <t>Which river was important to the Chera kingdom?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cholas</t>
+          <t>Kaveri</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Pandyas</t>
+          <t>Vaigai</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cheras</t>
+          <t>Periyar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Satavahanas</t>
+          <t>Pamba</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cheras</t>
+          <t>Periyar</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which work mentions the great floods that submerged the first Sangam?</t>
+          <t>Which foreign group is mentioned in Sangam texts as "Yavanas"?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>Greeks</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>Romans</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Iraiyanar Agapporul</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kalithogai</t>
+          <t>Arabs</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Iraiyanar Agapporul</t>
+          <t>Greeks</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which Sangam text deals with the ethics of life and is compared to the Gita?</t>
+          <t>Who was the famous poetess of the Sangam period?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Purananuru</t>
+          <t>Avvaiyar</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tolkappiyam</t>
+          <t>Kalidasa</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>Gargi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>Vishaka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>Avvaiyar</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The term 'Muvendar' refers to:</t>
+          <t>Which deity is most often praised in 'Paripadal'?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Three gods</t>
+          <t>Murugan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Three ports</t>
+          <t>Shiva</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Three kings</t>
+          <t>Vishnu</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Three texts</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Three kings</t>
+          <t>Vishnu</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which god is associated with the 'Kurinji' landscape in Sangam poetry?</t>
+          <t>Which king performed a “Rajasuyam” as per Sangam records?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Vishnu</t>
+          <t>Nedunjeliyan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Senguttuvan</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Murugan</t>
+          <t>Karikala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Perunarkilli</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Murugan</t>
+          <t>Perunarkilli</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which title did Chola kings often use?</t>
+          <t>The famous Tamil epic 'Silappatikaram' was composed by:</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Satyavadi</t>
+          <t>Ilango Adigal</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Vanavan</t>
+          <t>Avvaiyar</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Imayavaramban</t>
+          <t>Tolkappiyar</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chakravarti</t>
+          <t>Sattanar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Vanavan</t>
+          <t>Ilango Adigal</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which of the following was a chief occupation of the people in the Sangam age?</t>
+          <t>The Sangam period roughly corresponds to which time frame?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Blacksmithing</t>
+          <t>1000 BCE – 500 BCE</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>300 BCE – 300 CE</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Gold Mining</t>
+          <t>600 CE – 900 CE</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shipbuilding</t>
+          <t>900 CE – 1200 CE</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>300 BCE – 300 CE</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The most commonly mentioned god in Sangam literature is:</t>
+          <t>The term 'Velir' refers to:</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Vishnu</t>
+          <t>Commoners</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Shiva</t>
+          <t>Feudal chieftains</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Murugan</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Brahma</t>
+          <t>Slaves</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Murugan</t>
+          <t>Feudal chieftains</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The Sangam period saw trade with which Roman Emperor's era?</t>
+          <t>Which Sangam text contains information about the ideal king and his duties?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nero</t>
+          <t>Purananuru</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Augustus</t>
+          <t>Tolkappiyam</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Constantine</t>
+          <t>Pattinappalai</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Trajan</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Augustus</t>
+          <t>Purananuru</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which concept in Sangam poetry represents external experience like war, politics?</t>
+          <t>The Chera king Senguttuvan is associated with which legendary event?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Akam</t>
+          <t>Battle of Kalinga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Puram</t>
+          <t>Ratha Yatra</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bhakti</t>
+          <t>Worship of Kannagi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Aram</t>
+          <t>Battle of Hydaspes</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Puram</t>
+          <t>Worship of Kannagi</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tolkappiyam, a major work of Sangam literature, is primarily a treatise on:</t>
+          <t>'Akam' poetry deals with themes of:</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Medicine</t>
+          <t>War and Valor</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Love and Emotion</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Grammar</t>
+          <t>Religious Hymns</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Astronomy</t>
+          <t>Moral Ethics</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Grammar</t>
+          <t>Love and Emotion</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Sangam period roughly corresponds to which time frame?</t>
+          <t>Which Sangam king is believed to have imprisoned a Yavana trader?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1000 BCE – 500 BCE</t>
+          <t>Senguttuvan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>300 BCE – 300 CE</t>
+          <t>Karikala</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>600 CE – 900 CE</t>
+          <t>Nedunjeliyan</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>900 CE – 1200 CE</t>
+          <t>Perunarkilli</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>300 BCE – 300 CE</t>
+          <t>Nedunjeliyan</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which Sangam dynasty had its capital at Uraiyur?</t>
+          <t>Which work mentions the great floods that submerged the first Sangam?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cheras</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Pandyas</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cholas</t>
+          <t>Iraiyanar Agapporul</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pallavas</t>
+          <t>Kalithogai</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cholas</t>
+          <t>Iraiyanar Agapporul</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which Sangam king is said to have fed all poets in his court?</t>
+          <t>Which was the famous port of the Pandya kingdom?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Karikala</t>
+          <t>Uraiyur</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Nedunjeliyan</t>
+          <t>Tondi</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Uthiyan Cheralathan</t>
+          <t>Korkai</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Perunarkilli</t>
+          <t>Mamallapuram</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Uthiyan Cheralathan</t>
+          <t>Korkai</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Which landscape type is associated with lovers' separation in Sangam poetry?</t>
+          <t>The capital of the early Pandya kingdom during the Sangam age was:</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Palai</t>
+          <t>Kanchipuram</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Kurinji</t>
+          <t>Madurai</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Mullai</t>
+          <t>Uraiyur</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Marutham</t>
+          <t>Vanji</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Palai</t>
+          <t>Madurai</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which Sangam text is entirely devoted to the praise of kings and warfare?</t>
+          <t>The concept of 'Thinai' in Sangam literature relates to:</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Akananuru</t>
+          <t>Weapons</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Kalithogai</t>
+          <t>Landscape poetry</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Purananuru</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>Social caste</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Purananuru</t>
+          <t>Landscape poetry</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which foreign group is mentioned in Sangam texts as "Yavanas"?</t>
+          <t>The term 'Aram' in Sangam texts refers to:</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Greeks</t>
+          <t>Wealth</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Romans</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>Ethics</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Arabs</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Greeks</t>
+          <t>Ethics</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The term 'Vanigar' in Sangam texts refers to:</t>
+          <t>Which poem describes the city of Puhar in detail?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Soldiers</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Merchants</t>
+          <t>Pattinappalai</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Poets</t>
+          <t>Paripadal</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Merchants</t>
+          <t>Pattinappalai</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>How many Sangams are believed to have existed in ancient Tamil history?</t>
+          <t>Which Sangam king is said to have fed all poets in his court?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Karikala</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Nedunjeliyan</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Uthiyan Cheralathan</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Perunarkilli</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Uthiyan Cheralathan</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Sangam text 'Aingurunuru' belongs to which category?</t>
+          <t>The earliest mention of Tamil culture in foreign sources was by:</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Herodotus</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Grammar</t>
+          <t>Pliny the Elder</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Poetry</t>
+          <t>Ptolemy</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Drama</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poetry</t>
+          <t>Pliny the Elder</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which region is associated with the 'Mullai' landscape in Sangam literature?</t>
+          <t>Which metal was predominantly used for coinage during the Sangam Age?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Mountains</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Farmland</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which Sangam poet was known as the 'Friend of Nature'?</t>
+          <t>The Sangam assemblies were held in which temple?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avvaiyar</t>
+          <t>Meenakshi Temple</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Kapilar</t>
+          <t>Madurai Sangam Hall</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Nakkeerar</t>
+          <t>Koodal Azhagar Temple</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ilango Adigal</t>
+          <t>Thiruparankundram</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Kapilar</t>
+          <t>Koodal Azhagar Temple</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which foreign power established trade with Sangam-era Tamilakam?</t>
+          <t>Which Sangam dynasty had its capital at Uraiyur?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portuguese</t>
+          <t>Cheras</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Greeks</t>
+          <t>Pandyas</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>Cholas</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dutch</t>
+          <t>Pallavas</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Greeks</t>
+          <t>Cholas</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Who was the famous poetess of the Sangam period?</t>
+          <t>Who among the following was NOT a Sangam poet?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
+          <t>Kapilar</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
           <t>Avvaiyar</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Kalidasa</t>
-        </is>
-      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gargi</t>
+          <t>Ilango Adigal</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vishaka</t>
+          <t>Banabhatta</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Avvaiyar</t>
+          <t>Banabhatta</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Tamil work 'Manimekalai' is a sequel to:</t>
+          <t>Which Sangam text includes love poems?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
+          <t>Purananuru</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
           <t>Thirukkural</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Pattinappalai</t>
-        </is>
-      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>Akananuru</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2801,367 +2805,363 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>Akananuru</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The chief port of the Cholas during the Sangam period was:</t>
+          <t>The rulers of which dynasty used the bow and arrow as their emblem?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Puhar</t>
+          <t>Cholas</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Madurai</t>
+          <t>Pandyas</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Tondi</t>
+          <t>Cheras</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Korkai</t>
+          <t>Satavahanas</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Puhar</t>
+          <t>Cheras</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Who was the author of 'Manimekalai'?</t>
+          <t>Which of the following cities was submerged according to Sangam tradition?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ilango Adigal</t>
+          <t>Kanchi</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Avvaiyar</t>
+          <t>Puhar</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sattanar</t>
+          <t>Dwaraka</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tolkappiyar</t>
+          <t>Kumari Kandam</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sattanar</t>
+          <t>Kumari Kandam</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>'Akam' poetry deals with themes of:</t>
+          <t>What was the main theme of the text 'Purapporul Venba Malai'?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>War and Valor</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Love and Emotion</t>
+          <t>War</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Religious Hymns</t>
+          <t>Poetics</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Moral Ethics</t>
+          <t>Grammar</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Love and Emotion</t>
+          <t>War</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which foreign group were the "Yavanas" known for in Tamilakam?</t>
+          <t>Which landscape type is associated with lovers' separation in Sangam poetry?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Palai</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Kurinji</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Warfare</t>
+          <t>Mullai</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Philosophy</t>
+          <t>Marutham</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Palai</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which Tamil epic narrates the story of Kovalan and Kannagi?</t>
+          <t>The term 'Vanigar' in Sangam texts refers to:</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>Soldiers</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>Merchants</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Manimekalai</t>
+          <t>Poets</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Pattinappalai</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>Merchants</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which work mentions the story of a woman who burns down Madurai?</t>
+          <t>The city of Madurai is considered to be the center of which Sangam?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>First</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Manimekalai</t>
+          <t>Second</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Purananuru</t>
-        </is>
-      </c>
+          <t>Third</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>Third</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Sangam poems were compiled into:</t>
+          <t>Which of the following was a chief occupation of the people in the Sangam age?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>10 major works</t>
+          <t>Blacksmithing</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>5 minor works</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>18 major works</t>
+          <t>Gold Mining</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>12 minor works</t>
+          <t>Shipbuilding</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>18 major works</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which Sangam work describes the five-fold classification of land?</t>
+          <t>The Sangam literature was composed in which language?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Purananuru</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Tolkappiyam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Akananuru</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tolkappiyam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which Sangam poet was known for writing in praise of war heroes?</t>
+          <t>The Sangam age saw the use of which script?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Kapilar</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Paranar</t>
+          <t>Grantha</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Nakkeerar</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Avvaiyar</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Paranar</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The term 'Velir' refers to:</t>
+          <t>'Paripadal' is a Sangam text devoted to:</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Commoners</t>
+          <t>Heroism</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Feudal chieftains</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Religious hymns</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Slaves</t>
+          <t>Politics</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Feudal chieftains</t>
+          <t>Religious hymns</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>

--- a/Data/SangamPeriod.xlsx
+++ b/Data/SangamPeriod.xlsx
@@ -472,83 +472,83 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tolkappiyam, a major work of Sangam literature, is primarily a treatise on:</t>
+          <t>Which was the famous port of the Pandya kingdom?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Medicine</t>
+          <t>Uraiyur</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Tondi</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Grammar</t>
+          <t>Korkai</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Astronomy</t>
+          <t>Mamallapuram</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Grammar</t>
+          <t>Korkai</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What type of marriage was preferred in Sangam society?</t>
+          <t>Which Tamil epic narrates the story of Kovalan and Kannagi?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Arranged</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Swayamvara</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>Manimekalai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Endogamy</t>
+          <t>Pattinappalai</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which Sangam poet was known as the 'Friend of Nature'?</t>
+          <t>Who among the following composed war poems during the Sangam era?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -558,1797 +558,1793 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Kapilar</t>
+          <t>Kambar</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nakkeerar</t>
+          <t>Kalidasa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ilango Adigal</t>
+          <t>Bharavi</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kapilar</t>
+          <t>Avvaiyar</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which Sangam king is credited with conquering Sri Lanka?</t>
+          <t>What was the main theme of the text 'Purapporul Venba Malai'?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Karikala Chola</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nedunjeliyan</t>
+          <t>War</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Senguttuvan</t>
+          <t>Poetics</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Uthiyan Cheralathan</t>
+          <t>Grammar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Karikala Chola</t>
+          <t>War</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which concept in Sangam poetry represents external experience like war, politics?</t>
+          <t>Which Sangam poet was known as the 'Friend of Nature'?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Akam</t>
+          <t>Avvaiyar</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Puram</t>
+          <t>Kapilar</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bhakti</t>
+          <t>Nakkeerar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aram</t>
+          <t>Ilango Adigal</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Puram</t>
+          <t>Kapilar</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which foreign group were the "Yavanas" known for in Tamilakam?</t>
+          <t>Which of the following Tamil kingdoms was not part of the 'Muvendar'?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Cheras</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Cholas</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Warfare</t>
+          <t>Pandyas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Philosophy</t>
+          <t>Pallavas</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Pallavas</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>What was the term for land taxes in Sangam administration?</t>
+          <t>Which occupation was highly respected during the Sangam period?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irai</t>
+          <t>Pottery</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bhaga</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vetti</t>
+          <t>Fishing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Irai</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sangam poems were compiled into:</t>
+          <t>The famous Tamil epic 'Silappatikaram' was composed by:</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10 major works</t>
+          <t>Ilango Adigal</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5 minor works</t>
+          <t>Avvaiyar</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18 major works</t>
+          <t>Tolkappiyar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>12 minor works</t>
+          <t>Sattanar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>18 major works</t>
+          <t>Ilango Adigal</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which literary work gives an account of Karikala Chola’s rule?</t>
+          <t>The Sangam assemblies were held in which temple?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Manimekalai</t>
+          <t>Meenakshi Temple</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pattinappalai</t>
+          <t>Madurai Sangam Hall</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>Koodal Azhagar Temple</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paripadal</t>
+          <t>Thiruparankundram</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pattinappalai</t>
+          <t>Koodal Azhagar Temple</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The symbol of the Chola dynasty was:</t>
+          <t>The chief port of the Cholas during the Sangam period was:</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Puhar</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bow</t>
+          <t>Madurai</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Tondi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Korkai</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Puhar</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The most commonly mentioned god in Sangam literature is:</t>
+          <t>The term 'Velir' refers to:</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vishnu</t>
+          <t>Commoners</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Shiva</t>
+          <t>Feudal chieftains</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Murugan</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brahma</t>
+          <t>Slaves</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Murugan</t>
+          <t>Feudal chieftains</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The chief port of the Cholas during the Sangam period was:</t>
+          <t>What was the role of 'Arasu' in Sangam polity?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Puhar</t>
+          <t>Poet</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Madurai</t>
+          <t>Judge</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tondi</t>
+          <t>King</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korkai</t>
+          <t>Priest</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Puhar</t>
+          <t>King</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Sangam literature is divided into:</t>
+          <t>The term 'Muvendar' refers to:</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Religious &amp; Scientific</t>
+          <t>Three gods</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Historical &amp; Fictional</t>
+          <t>Three ports</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Akam &amp; Puram</t>
+          <t>Three kings</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>North &amp; South</t>
+          <t>Three texts</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Akam &amp; Puram</t>
+          <t>Three kings</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which work mentions the story of a woman who burns down Madurai?</t>
+          <t>What was the title of the Chola king Karikala?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>Vanavan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Manimekalai</t>
+          <t>Imayavaramban</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>Senguttuvan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Purananuru</t>
+          <t>Karikalan</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>Karikalan</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which Sangam king defeated the combined forces of Cheras and Pandyas?</t>
+          <t>Who among the following was NOT a Sangam poet?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Karikala Chola</t>
+          <t>Kapilar</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Senguttuvan</t>
+          <t>Avvaiyar</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Perunarkilli</t>
+          <t>Ilango Adigal</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nedunjeliyan</t>
+          <t>Banabhatta</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Karikala Chola</t>
+          <t>Banabhatta</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which of the following was a famous Sangam port city?</t>
+          <t>Which work mentions the story of a woman who burns down Madurai?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kanchipuram</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Puhar</t>
+          <t>Manimekalai</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Madurai</t>
+          <t>Purananuru</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Puhar</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>What was the title of the Chola king Karikala?</t>
+          <t>Which Sangam king defeated the combined forces of Cheras and Pandyas?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vanavan</t>
+          <t>Karikala Chola</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Imayavaramban</t>
+          <t>Senguttuvan</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Senguttuvan</t>
+          <t>Perunarkilli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Karikalan</t>
+          <t>Nedunjeliyan</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Karikalan</t>
+          <t>Karikala Chola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which Sangam text deals with the ethics of life and is compared to the Gita?</t>
+          <t>Which Sangam king is credited with conquering Sri Lanka?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Purananuru</t>
+          <t>Karikala Chola</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tolkappiyam</t>
+          <t>Nedunjeliyan</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>Senguttuvan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>Uthiyan Cheralathan</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>Karikala Chola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which class dominated Sangam politics and economy?</t>
+          <t>Which foreign power established trade with Sangam-era Tamilakam?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Portuguese</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Kshatriyas</t>
+          <t>Greeks</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Velirs</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Merchants</t>
+          <t>Dutch</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Velirs</t>
+          <t>Greeks</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which god is associated with the 'Kurinji' landscape in Sangam poetry?</t>
+          <t>Which Sangam text is entirely devoted to the praise of kings and warfare?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Vishnu</t>
+          <t>Akananuru</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Kalithogai</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Murugan</t>
+          <t>Purananuru</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Murugan</t>
+          <t>Purananuru</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The term 'Muvendar' refers to:</t>
+          <t>The Chera king Senguttuvan is associated with which legendary event?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Three gods</t>
+          <t>Battle of Kalinga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Three ports</t>
+          <t>Ratha Yatra</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Three kings</t>
+          <t>Worship of Kannagi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Three texts</t>
+          <t>Battle of Hydaspes</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Three kings</t>
+          <t>Worship of Kannagi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Sangam period saw trade with which Roman Emperor's era?</t>
+          <t>What type of marriage was preferred in Sangam society?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nero</t>
+          <t>Arranged</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Augustus</t>
+          <t>Swayamvara</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Constantine</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trajan</t>
+          <t>Endogamy</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Augustus</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which title did Chola kings often use?</t>
+          <t>Which Sangam text contains information about the ideal king and his duties?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Satyavadi</t>
+          <t>Purananuru</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Vanavan</t>
+          <t>Tolkappiyam</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Imayavaramban</t>
+          <t>Pattinappalai</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chakravarti</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Vanavan</t>
+          <t>Purananuru</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which occupation was highly respected during the Sangam period?</t>
+          <t>Which Sangam king is believed to have imprisoned a Yavana trader?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pottery</t>
+          <t>Senguttuvan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Karikala</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Nedunjeliyan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Perunarkilli</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Nedunjeliyan</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which Sangam text describes trade activities in detail?</t>
+          <t>Which Sangam age king was known as "Imayavaramban"?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>Karikala Chola</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Pattinappalai</t>
+          <t>Senguttuvan</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Akananuru</t>
+          <t>Nedunjeliyan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tolkappiyam</t>
+          <t>Uthiyan Cheralathan</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pattinappalai</t>
+          <t>Senguttuvan</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which Tamil epic narrates the story of Kovalan and Kannagi?</t>
+          <t>Which concept in Sangam poetry represents external experience like war, politics?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>Akam</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>Puram</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Manimekalai</t>
+          <t>Bhakti</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pattinappalai</t>
+          <t>Aram</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>Puram</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which Sangam text is entirely devoted to the praise of kings and warfare?</t>
+          <t>Which work mentions the great floods that submerged the first Sangam?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Akananuru</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>Silappatikaram</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Iraiyanar Agapporul</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>Kalithogai</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Purananuru</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Thirukkural</t>
-        </is>
-      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Purananuru</t>
+          <t>Iraiyanar Agapporul</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which Sangam poet was known for writing in praise of war heroes?</t>
+          <t>The Tamil work 'Manimekalai' is a sequel to:</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kapilar</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Paranar</t>
+          <t>Pattinappalai</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nakkeerar</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Avvaiyar</t>
+          <t>Tolkappiyam</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Paranar</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>What was the role of 'Arasu' in Sangam polity?</t>
+          <t>Which poem describes the city of Puhar in detail?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poet</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Judge</t>
+          <t>Pattinappalai</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>King</t>
+          <t>Paripadal</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Priest</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>King</t>
+          <t>Pattinappalai</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which Sangam port had Roman amphorae and coins excavated?</t>
+          <t>The concept of 'Thinai' in Sangam literature relates to:</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Puhar</t>
+          <t>Weapons</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Korkai</t>
+          <t>Landscape poetry</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tondi</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Arikamedu</t>
+          <t>Social caste</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Arikamedu</t>
+          <t>Landscape poetry</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which foreign power established trade with Sangam-era Tamilakam?</t>
+          <t>Which god is associated with the 'Kurinji' landscape in Sangam poetry?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portuguese</t>
+          <t>Vishnu</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Greeks</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>Murugan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dutch</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Greeks</t>
+          <t>Murugan</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Who among the following composed war poems during the Sangam era?</t>
+          <t>Which Sangam text describes trade activities in detail?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avvaiyar</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Kambar</t>
+          <t>Pattinappalai</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kalidasa</t>
+          <t>Akananuru</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bharavi</t>
+          <t>Tolkappiyam</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Avvaiyar</t>
+          <t>Pattinappalai</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which of the following Tamil kingdoms was not part of the 'Muvendar'?</t>
+          <t>Which Sangam text deals with the ethics of life and is compared to the Gita?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cheras</t>
+          <t>Purananuru</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cholas</t>
+          <t>Tolkappiyam</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pandyas</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pallavas</t>
+          <t>Silappatikaram</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pallavas</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which Sangam age king was known as "Imayavaramban"?</t>
+          <t>The Sangam age saw the use of which script?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Karikala Chola</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Senguttuvan</t>
+          <t>Grantha</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nedunjeliyan</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Uthiyan Cheralathan</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Senguttuvan</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which region is associated with the 'Mullai' landscape in Sangam literature?</t>
+          <t>Which of the following was a chief occupation of the people in the Sangam age?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mountains</t>
+          <t>Blacksmithing</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Farmland</t>
+          <t>Gold Mining</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Shipbuilding</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Who was the author of 'Manimekalai'?</t>
+          <t>Which foreign group were the "Yavanas" known for in Tamilakam?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ilango Adigal</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Avvaiyar</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sattanar</t>
+          <t>Warfare</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tolkappiyar</t>
+          <t>Philosophy</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sattanar</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Sangam text 'Aingurunuru' belongs to which category?</t>
+          <t>The Sangam literature was composed in which language?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Grammar</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Poetry</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Drama</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poetry</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Tamil work 'Manimekalai' is a sequel to:</t>
+          <t>Which metal was predominantly used for coinage during the Sangam Age?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Pattinappalai</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tolkappiyam</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which Sangam work describes the five-fold classification of land?</t>
+          <t>Which of the following was a famous Sangam port city?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>Kanchipuram</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Purananuru</t>
+          <t>Puhar</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tolkappiyam</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Akananuru</t>
+          <t>Madurai</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tolkappiyam</t>
+          <t>Puhar</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>How many Sangams are believed to have existed in ancient Tamil history?</t>
+          <t>Which king performed a “Rajasuyam” as per Sangam records?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Nedunjeliyan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Senguttuvan</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Karikala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Perunarkilli</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Perunarkilli</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which river was important to the Chera kingdom?</t>
+          <t>Who was the author of 'Manimekalai'?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kaveri</t>
+          <t>Ilango Adigal</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Vaigai</t>
+          <t>Avvaiyar</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Periyar</t>
+          <t>Sattanar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pamba</t>
+          <t>Tolkappiyar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Periyar</t>
+          <t>Sattanar</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which foreign group is mentioned in Sangam texts as "Yavanas"?</t>
+          <t>Which title did Chola kings often use?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Greeks</t>
+          <t>Satyavadi</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Romans</t>
+          <t>Vanavan</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>Imayavaramban</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Arabs</t>
+          <t>Chakravarti</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Greeks</t>
+          <t>Vanavan</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Who was the famous poetess of the Sangam period?</t>
+          <t>Tolkappiyam, a major work of Sangam literature, is primarily a treatise on:</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avvaiyar</t>
+          <t>Medicine</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Kalidasa</t>
+          <t>Politics</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Gargi</t>
+          <t>Grammar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vishaka</t>
+          <t>Astronomy</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Avvaiyar</t>
+          <t>Grammar</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which deity is most often praised in 'Paripadal'?</t>
+          <t>The rulers of which dynasty used the bow and arrow as their emblem?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Murugan</t>
+          <t>Cholas</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Shiva</t>
+          <t>Pandyas</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Vishnu</t>
+          <t>Cheras</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Satavahanas</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Vishnu</t>
+          <t>Cheras</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which king performed a “Rajasuyam” as per Sangam records?</t>
+          <t>Which deity is most often praised in 'Paripadal'?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nedunjeliyan</t>
+          <t>Murugan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Senguttuvan</t>
+          <t>Shiva</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Karikala</t>
+          <t>Vishnu</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Perunarkilli</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Perunarkilli</t>
+          <t>Vishnu</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The famous Tamil epic 'Silappatikaram' was composed by:</t>
+          <t>'Paripadal' is a Sangam text devoted to:</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ilango Adigal</t>
+          <t>Heroism</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Avvaiyar</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tolkappiyar</t>
+          <t>Religious hymns</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sattanar</t>
+          <t>Politics</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ilango Adigal</t>
+          <t>Religious hymns</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The Sangam period roughly corresponds to which time frame?</t>
+          <t>Which Sangam port had Roman amphorae and coins excavated?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1000 BCE – 500 BCE</t>
+          <t>Puhar</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>300 BCE – 300 CE</t>
+          <t>Korkai</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>600 CE – 900 CE</t>
+          <t>Tondi</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>900 CE – 1200 CE</t>
+          <t>Arikamedu</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>300 BCE – 300 CE</t>
+          <t>Arikamedu</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The term 'Velir' refers to:</t>
+          <t>'Akam' poetry deals with themes of:</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Commoners</t>
+          <t>War and Valor</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Feudal chieftains</t>
+          <t>Love and Emotion</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Religious Hymns</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Slaves</t>
+          <t>Moral Ethics</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Feudal chieftains</t>
+          <t>Love and Emotion</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which Sangam text contains information about the ideal king and his duties?</t>
+          <t>Which Sangam poet was known for writing in praise of war heroes?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Purananuru</t>
+          <t>Kapilar</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Tolkappiyam</t>
+          <t>Paranar</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Pattinappalai</t>
+          <t>Nakkeerar</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>Avvaiyar</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Purananuru</t>
+          <t>Paranar</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Chera king Senguttuvan is associated with which legendary event?</t>
+          <t>Which landscape type is associated with lovers' separation in Sangam poetry?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Battle of Kalinga</t>
+          <t>Palai</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Ratha Yatra</t>
+          <t>Kurinji</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Worship of Kannagi</t>
+          <t>Mullai</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Battle of Hydaspes</t>
+          <t>Marutham</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Worship of Kannagi</t>
+          <t>Palai</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>'Akam' poetry deals with themes of:</t>
+          <t>Which class dominated Sangam politics and economy?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>War and Valor</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Love and Emotion</t>
+          <t>Kshatriyas</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Religious Hymns</t>
+          <t>Velirs</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Moral Ethics</t>
+          <t>Merchants</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Love and Emotion</t>
+          <t>Velirs</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which Sangam king is believed to have imprisoned a Yavana trader?</t>
+          <t>The city of Madurai is considered to be the center of which Sangam?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Senguttuvan</t>
+          <t>First</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Karikala</t>
+          <t>Second</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Nedunjeliyan</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Perunarkilli</t>
-        </is>
-      </c>
+          <t>Third</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nedunjeliyan</t>
+          <t>Third</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which work mentions the great floods that submerged the first Sangam?</t>
+          <t>Which Sangam work describes the five-fold classification of land?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2358,130 +2354,130 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>Purananuru</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Iraiyanar Agapporul</t>
+          <t>Tolkappiyam</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kalithogai</t>
+          <t>Akananuru</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Iraiyanar Agapporul</t>
+          <t>Tolkappiyam</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which was the famous port of the Pandya kingdom?</t>
+          <t>Which Sangam king is said to have fed all poets in his court?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Uraiyur</t>
+          <t>Karikala</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Tondi</t>
+          <t>Nedunjeliyan</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Korkai</t>
+          <t>Uthiyan Cheralathan</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mamallapuram</t>
+          <t>Perunarkilli</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Korkai</t>
+          <t>Uthiyan Cheralathan</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>The capital of the early Pandya kingdom during the Sangam age was:</t>
+          <t>The earliest mention of Tamil culture in foreign sources was by:</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kanchipuram</t>
+          <t>Herodotus</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Madurai</t>
+          <t>Pliny the Elder</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Uraiyur</t>
+          <t>Ptolemy</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vanji</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Madurai</t>
+          <t>Pliny the Elder</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The concept of 'Thinai' in Sangam literature relates to:</t>
+          <t>The capital of the early Pandya kingdom during the Sangam age was:</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Weapons</t>
+          <t>Kanchipuram</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Landscape poetry</t>
+          <t>Madurai</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Uraiyur</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Social caste</t>
+          <t>Vanji</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Landscape poetry</t>
+          <t>Madurai</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
@@ -2524,644 +2520,648 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which poem describes the city of Puhar in detail?</t>
+          <t>Who was the famous poetess of the Sangam period?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>Avvaiyar</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Pattinappalai</t>
+          <t>Kalidasa</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Paripadal</t>
+          <t>Gargi</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Silappatikaram</t>
+          <t>Vishaka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pattinappalai</t>
+          <t>Avvaiyar</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which Sangam king is said to have fed all poets in his court?</t>
+          <t>Which Sangam text includes love poems?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Karikala</t>
+          <t>Purananuru</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Nedunjeliyan</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Uthiyan Cheralathan</t>
+          <t>Akananuru</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Perunarkilli</t>
+          <t>Tolkappiyam</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Uthiyan Cheralathan</t>
+          <t>Akananuru</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The earliest mention of Tamil culture in foreign sources was by:</t>
+          <t>Sangam poems were compiled into:</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Herodotus</t>
+          <t>10 major works</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Pliny the Elder</t>
+          <t>5 minor works</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ptolemy</t>
+          <t>18 major works</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>12 minor works</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pliny the Elder</t>
+          <t>18 major works</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which metal was predominantly used for coinage during the Sangam Age?</t>
+          <t>How many Sangams are believed to have existed in ancient Tamil history?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Sangam assemblies were held in which temple?</t>
+          <t>The Sangam period roughly corresponds to which time frame?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Meenakshi Temple</t>
+          <t>1000 BCE – 500 BCE</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Madurai Sangam Hall</t>
+          <t>300 BCE – 300 CE</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Koodal Azhagar Temple</t>
+          <t>600 CE – 900 CE</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Thiruparankundram</t>
+          <t>900 CE – 1200 CE</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Koodal Azhagar Temple</t>
+          <t>300 BCE – 300 CE</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which Sangam dynasty had its capital at Uraiyur?</t>
+          <t>What was the term for land taxes in Sangam administration?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cheras</t>
+          <t>Irai</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Pandyas</t>
+          <t>Bhaga</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Cholas</t>
+          <t>Bali</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pallavas</t>
+          <t>Vetti</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cholas</t>
+          <t>Irai</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Who among the following was NOT a Sangam poet?</t>
+          <t>Which region is associated with the 'Mullai' landscape in Sangam literature?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Kapilar</t>
+          <t>Mountains</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Avvaiyar</t>
+          <t>Forest</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ilango Adigal</t>
+          <t>Farmland</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Banabhatta</t>
+          <t>Coast</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Banabhatta</t>
+          <t>Forest</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which Sangam text includes love poems?</t>
+          <t>Which river was important to the Chera kingdom?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Purananuru</t>
+          <t>Kaveri</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Thirukkural</t>
+          <t>Vaigai</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Akananuru</t>
+          <t>Periyar</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tolkappiyam</t>
+          <t>Pamba</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Akananuru</t>
+          <t>Periyar</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The rulers of which dynasty used the bow and arrow as their emblem?</t>
+          <t>Which literary work gives an account of Karikala Chola’s rule?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cholas</t>
+          <t>Manimekalai</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Pandyas</t>
+          <t>Pattinappalai</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cheras</t>
+          <t>Thirukkural</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Satavahanas</t>
+          <t>Paripadal</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cheras</t>
+          <t>Pattinappalai</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which of the following cities was submerged according to Sangam tradition?</t>
+          <t>The Sangam text 'Aingurunuru' belongs to which category?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Kanchi</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Puhar</t>
+          <t>Grammar</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dwaraka</t>
+          <t>Poetry</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kumari Kandam</t>
+          <t>Drama</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Kumari Kandam</t>
+          <t>Poetry</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>What was the main theme of the text 'Purapporul Venba Malai'?</t>
+          <t>Which of the following cities was submerged according to Sangam tradition?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>Kanchi</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>War</t>
+          <t>Puhar</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Poetics</t>
+          <t>Dwaraka</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grammar</t>
+          <t>Kumari Kandam</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>War</t>
+          <t>Kumari Kandam</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which landscape type is associated with lovers' separation in Sangam poetry?</t>
+          <t>The most commonly mentioned god in Sangam literature is:</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Palai</t>
+          <t>Vishnu</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Kurinji</t>
+          <t>Shiva</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Mullai</t>
+          <t>Murugan</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Marutham</t>
+          <t>Brahma</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Palai</t>
+          <t>Murugan</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The term 'Vanigar' in Sangam texts refers to:</t>
+          <t>The Sangam literature is divided into:</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Soldiers</t>
+          <t>Religious &amp; Scientific</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Merchants</t>
+          <t>Historical &amp; Fictional</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Poets</t>
+          <t>Akam &amp; Puram</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>North &amp; South</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Merchants</t>
+          <t>Akam &amp; Puram</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The city of Madurai is considered to be the center of which Sangam?</t>
+          <t>The Sangam period saw trade with which Roman Emperor's era?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>First</t>
+          <t>Nero</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Second</t>
+          <t>Augustus</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Third</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
+          <t>Constantine</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Trajan</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Third</t>
+          <t>Augustus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which of the following was a chief occupation of the people in the Sangam age?</t>
+          <t>The term 'Vanigar' in Sangam texts refers to:</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Blacksmithing</t>
+          <t>Soldiers</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Merchants</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Gold Mining</t>
+          <t>Poets</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Shipbuilding</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Merchants</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The Sangam literature was composed in which language?</t>
+          <t>The symbol of the Chola dynasty was:</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Fish</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Bow</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The Sangam age saw the use of which script?</t>
+          <t>Which Sangam dynasty had its capital at Uraiyur?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>Cheras</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Grantha</t>
+          <t>Pandyas</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Cholas</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Pallavas</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Cholas</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>'Paripadal' is a Sangam text devoted to:</t>
+          <t>Which foreign group is mentioned in Sangam texts as "Yavanas"?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Heroism</t>
+          <t>Greeks</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>Romans</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Religious hymns</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Arabs</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Religious hymns</t>
+          <t>Greeks</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
